--- a/backend/api/static/api/student_import_template.xlsx
+++ b/backend/api/static/api/student_import_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -460,17 +460,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>section_code</t>
+          <t>username</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>subject_code</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -495,9 +500,12 @@
           <t>avery.example@example.invalid</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="b">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/api/static/api/student_import_template.xlsx
+++ b/backend/api/static/api/student_import_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -440,42 +440,32 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>Student ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>subject_code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>active</t>
+          <t>Subject</t>
         </is>
       </c>
     </row>
@@ -500,13 +490,10 @@
           <t>avery.example@example.invalid</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>student</t>
         </is>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
